--- a/exit_interview_templates/030_employee_exit_communication_form--exit_interview_templates.xlsx
+++ b/exit_interview_templates/030_employee_exit_communication_form--exit_interview_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'new_opportunity'}</t>
+          <t>new_opportunity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'New opportunity'}</t>
+          <t>New opportunity</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'career_change'}</t>
+          <t>career_change</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Career Change'}</t>
+          <t>Career Change</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'job_not_available'}</t>
+          <t>job_not_available</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Job not available'}</t>
+          <t>Job not available</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'health_issues'}</t>
+          <t>health_issues</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Health issues'}</t>
+          <t>Health issues</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'family_obligations'}</t>
+          <t>family_obligations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Family obligations'}</t>
+          <t>Family obligations</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'helped_others'}</t>
+          <t>helped_others</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Helped others'}</t>
+          <t>Helped others</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'improved_processes'}</t>
+          <t>improved_processes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Improved processes'}</t>
+          <t>Improved processes</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'increased_productivity'}</t>
+          <t>increased_productivity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Increased productivity'}</t>
+          <t>Increased productivity</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'reduced_costs'}</t>
+          <t>reduced_costs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Reduced costs'}</t>
+          <t>Reduced costs</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'regular_meetings'}</t>
+          <t>regular_meetings</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Regular meetings'}</t>
+          <t>Regular meetings</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'irregular_meetings'}</t>
+          <t>irregular_meetings</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Irregular meetings'}</t>
+          <t>Irregular meetings</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'e-mail'}</t>
+          <t>e-mail</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'E-mail'}</t>
+          <t>E-mail</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'phone_calls'}</t>
+          <t>phone_calls</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Phone calls'}</t>
+          <t>Phone calls</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'text_messages'}</t>
+          <t>text_messages</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Text messages'}</t>
+          <t>Text messages</t>
         </is>
       </c>
     </row>
